--- a/Excel/Triage_y_Evaluacion_Basica_Enfermeria.xlsx
+++ b/Excel/Triage_y_Evaluacion_Basica_Enfermeria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Hernán\Desktop\Administracion HernanMayol\Python_ISSUNNE\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C52F857-890D-458D-B639-5F0026AEBE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A88C3D-AB13-4093-996B-0DF91CC12572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -313,6 +313,47 @@
   </cellStyles>
   <dxfs count="36">
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="6"/>
@@ -381,79 +422,38 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="166" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -559,50 +559,50 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre y Apellido" dataDxfId="33"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Peso (kg)"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Talla (m)" dataDxfId="32"/>
-    <tableColumn id="16" xr3:uid="{EB62B56F-A273-4996-9B57-F6B36FE64967}" name="IMC" dataDxfId="13">
+    <tableColumn id="16" xr3:uid="{EB62B56F-A273-4996-9B57-F6B36FE64967}" name="IMC" dataDxfId="31">
       <calculatedColumnFormula>IFERROR(E2/(Registro_Triage!F2^2),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A3612F64-308B-47A4-B163-BDE1CA9C2210}" name="Sexo" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Perímetro Cintura (m)" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Presión Sistólica 1" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{C8E53D07-3C42-4C64-A28A-436C2D390692}" name="Presión Diastólica 1" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Presión Sistólica 2" dataDxfId="29"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Presión Diastólica 2" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Frecuencia Cardíaca" dataDxfId="28"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Glucemia (mg/dl)" dataDxfId="27"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Saturación O2 (%)" dataDxfId="26"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Observaciones/Comentarios" dataDxfId="25"/>
+    <tableColumn id="19" xr3:uid="{A3612F64-308B-47A4-B163-BDE1CA9C2210}" name="Sexo" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Perímetro Cintura (m)" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Presión Sistólica 1" dataDxfId="28"/>
+    <tableColumn id="17" xr3:uid="{C8E53D07-3C42-4C64-A28A-436C2D390692}" name="Presión Diastólica 1" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Presión Sistólica 2" dataDxfId="26"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Presión Diastólica 2" dataDxfId="25"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Frecuencia Cardíaca" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Glucemia (mg/dl)" dataDxfId="23"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Saturación O2 (%)" dataDxfId="22"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Observaciones/Comentarios" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_Calculos" displayName="Tabla_Calculos" ref="A1:L12" totalsRowShown="0" headerRowDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_Calculos" displayName="Tabla_Calculos" ref="A1:L12" totalsRowShown="0" headerRowDxfId="12">
   <autoFilter ref="A1:L12" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID Paciente" dataDxfId="23">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID Paciente" dataDxfId="11">
       <calculatedColumnFormula>Tabla_Triage[[#This Row],[ID Paciente]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fecha" dataDxfId="22">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fecha" dataDxfId="10">
       <calculatedColumnFormula>Tabla_Triage[[#This Row],[Fecha]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{5B10D3AB-37DC-4AC1-B3E1-411DF10FD1D5}" name="Sexo" dataDxfId="21">
+    <tableColumn id="13" xr3:uid="{5B10D3AB-37DC-4AC1-B3E1-411DF10FD1D5}" name="Sexo" dataDxfId="9">
       <calculatedColumnFormula>Tabla_Triage[[#This Row],[Sexo]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="IMC" dataDxfId="20">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="IMC" dataDxfId="8">
       <calculatedColumnFormula>IFERROR(Registro_Triage!E2/(Registro_Triage!F2^2),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Clasificación IMC" dataDxfId="19">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Clasificación IMC" dataDxfId="7">
       <calculatedColumnFormula>IF(D2="","",IF(D2&lt;18.5,"Bajo peso",IF(D2&lt;25,"Normal",IF(D2&lt;30,"Sobrepeso","Obesidad"))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Presión Sistólica Promedio" dataDxfId="10">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Presión Sistólica Promedio" dataDxfId="6">
       <calculatedColumnFormula>IF(COUNT(Registro_Triage!J2, Registro_Triage!L2)=0, "", AVERAGE(Registro_Triage!J2, Registro_Triage!L2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Presión Diastólica Promedio" dataDxfId="9">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Presión Diastólica Promedio" dataDxfId="5">
       <calculatedColumnFormula>IF(COUNT(Registro_Triage!K2, Registro_Triage!M2)=0, "", AVERAGE(Registro_Triage!K2, Registro_Triage!M2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Riesgo Inicial" dataDxfId="18">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Riesgo Inicial" dataDxfId="4">
       <calculatedColumnFormula>IF(
 OR(I2="",J2="",K2=""),
 "",
@@ -613,10 +613,10 @@
 )
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{2AA4B4F3-ACC1-459E-87D6-8904E584A3B4}" name="ALERTA_O2" dataDxfId="17">
+    <tableColumn id="8" xr3:uid="{2AA4B4F3-ACC1-459E-87D6-8904E584A3B4}" name="ALERTA_O2" dataDxfId="3">
       <calculatedColumnFormula>IF(OR(Registro_Triage!P2="", NOT(ISNUMBER(Registro_Triage!P2*1))), "", IF(Registro_Triage!P2*1 &lt; VLOOKUP("Saturación O2 Normal", Referencias!$A:$C, 2, 0), "ALTO", "NORMAL"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{F79C9761-E006-46E6-A449-D718B8CB107E}" name="ALERTA_Presion" dataDxfId="16">
+    <tableColumn id="9" xr3:uid="{F79C9761-E006-46E6-A449-D718B8CB107E}" name="ALERTA_Presion" dataDxfId="2">
       <calculatedColumnFormula>IF(
 OR(
 F2 &gt; VLOOKUP("Presión Sistólica Normal",Referencias!A:C,3,FALSE),
@@ -626,7 +626,7 @@
 0
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1C56DDB5-870B-4F3E-8434-528DCB879C08}" name="ALERTA_IMC" dataDxfId="15">
+    <tableColumn id="10" xr3:uid="{1C56DDB5-870B-4F3E-8434-528DCB879C08}" name="ALERTA_IMC" dataDxfId="1">
       <calculatedColumnFormula>IF(
 OR(
 D2 &lt; VLOOKUP("IMC Normal",Referencias!A:C,2,FALSE),
@@ -636,7 +636,7 @@
 0
 )</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{5491193D-3D2C-4BB1-9F1D-AF9F5FC6BE37}" name="ALERTA_Cintura" dataDxfId="14">
+    <tableColumn id="12" xr3:uid="{5491193D-3D2C-4BB1-9F1D-AF9F5FC6BE37}" name="ALERTA_Cintura" dataDxfId="0">
       <calculatedColumnFormula>IF(
 OR(Registro_Triage!H2="",Registro_Triage!I2=""),
 "",
@@ -1612,7 +1612,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -2087,7 +2087,7 @@
         <v>23.510204081632654</v>
       </c>
       <c r="E7" s="9" t="str">
-        <f>IF(D7="","",IF(D7&lt;18.5,"Bajo peso",IF(D7&lt;25,"Normal",IF(D7&lt;30,"Sobrepeso","Obesidad"))))</f>
+        <f t="shared" ref="E7:E12" si="2">IF(D7="","",IF(D7&lt;18.5,"Bajo peso",IF(D7&lt;25,"Normal",IF(D7&lt;30,"Sobrepeso","Obesidad"))))</f>
         <v>Normal</v>
       </c>
       <c r="F7" s="11">
@@ -2164,7 +2164,7 @@
         <v>30.119375573921033</v>
       </c>
       <c r="E8" s="9" t="str">
-        <f>IF(D8="","",IF(D8&lt;18.5,"Bajo peso",IF(D8&lt;25,"Normal",IF(D8&lt;30,"Sobrepeso","Obesidad"))))</f>
+        <f t="shared" si="2"/>
         <v>Obesidad</v>
       </c>
       <c r="F8" s="11">
@@ -2241,7 +2241,7 @@
         <v>32.871972318339104</v>
       </c>
       <c r="E9" s="9" t="str">
-        <f>IF(D9="","",IF(D9&lt;18.5,"Bajo peso",IF(D9&lt;25,"Normal",IF(D9&lt;30,"Sobrepeso","Obesidad"))))</f>
+        <f t="shared" si="2"/>
         <v>Obesidad</v>
       </c>
       <c r="F9" s="11">
@@ -2318,7 +2318,7 @@
         <v>29.411764705882355</v>
       </c>
       <c r="E10" s="9" t="str">
-        <f>IF(D10="","",IF(D10&lt;18.5,"Bajo peso",IF(D10&lt;25,"Normal",IF(D10&lt;30,"Sobrepeso","Obesidad"))))</f>
+        <f t="shared" si="2"/>
         <v>Sobrepeso</v>
       </c>
       <c r="F10" s="11">
@@ -2395,7 +2395,7 @@
         <v>21.513858510523864</v>
       </c>
       <c r="E11" s="9" t="str">
-        <f>IF(D11="","",IF(D11&lt;18.5,"Bajo peso",IF(D11&lt;25,"Normal",IF(D11&lt;30,"Sobrepeso","Obesidad"))))</f>
+        <f t="shared" si="2"/>
         <v>Normal</v>
       </c>
       <c r="F11" s="11">
@@ -2472,7 +2472,7 @@
         <v>23.629489603024574</v>
       </c>
       <c r="E12" s="9" t="str">
-        <f>IF(D12="","",IF(D12&lt;18.5,"Bajo peso",IF(D12&lt;25,"Normal",IF(D12&lt;30,"Sobrepeso","Obesidad"))))</f>
+        <f t="shared" si="2"/>
         <v>Normal</v>
       </c>
       <c r="F12" s="11">
@@ -2547,32 +2547,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="BAJO">
+    <cfRule type="containsText" dxfId="20" priority="6" operator="containsText" text="BAJO">
       <formula>NOT(ISERROR(SEARCH("BAJO",H1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="MEDIO">
+    <cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="MEDIO">
       <formula>NOT(ISERROR(SEARCH("MEDIO",H1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="8" operator="containsText" text="ALTO">
+    <cfRule type="containsText" dxfId="18" priority="8" operator="containsText" text="ALTO">
       <formula>NOT(ISERROR(SEARCH("ALTO",H1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="ALTO">
+    <cfRule type="containsText" dxfId="17" priority="4" operator="containsText" text="ALTO">
       <formula>NOT(ISERROR(SEARCH("ALTO",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="NORMAL">
+    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="NORMAL">
       <formula>NOT(ISERROR(SEARCH("NORMAL",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Alto riesgo">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="Alto riesgo">
       <formula>NOT(ISERROR(SEARCH("Alto riesgo",L1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Riesgo aumentado">
+    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="Riesgo aumentado">
       <formula>NOT(ISERROR(SEARCH("Riesgo aumentado",L1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Normal">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="Normal">
       <formula>NOT(ISERROR(SEARCH("Normal",L1)))</formula>
     </cfRule>
   </conditionalFormatting>
